--- a/data/daily_metrics_week_2.xlsx
+++ b/data/daily_metrics_week_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3841b178c28d2367/Documents/GitHub/marketing-impact-lab/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_AD4D1D646341095ACB7000EC6510C6CE693EDF13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96B96BB2-5026-4511-8A1E-1830F7B1BABA}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="11_AD4D1D646341095ACB7000EC6510C6CE693EDF13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F370ED0C-A740-4B63-97E4-94C6503B3583}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25755" yWindow="3060" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="17">
   <si>
     <t>date</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>none</t>
+  </si>
+  <si>
+    <t>mil_wk1_project_post</t>
+  </si>
+  <si>
+    <t>google/organic</t>
   </si>
 </sst>
 </file>
@@ -132,6 +138,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,14 +407,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -460,8 +470,8 @@
       <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>1</v>
+      <c r="E2" t="s">
+        <v>15</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -495,8 +505,8 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
-        <v>0</v>
+      <c r="E3" t="s">
+        <v>15</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -530,8 +540,8 @@
       <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="E4">
-        <v>0</v>
+      <c r="E4" t="s">
+        <v>15</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -565,8 +575,8 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5">
-        <v>1</v>
+      <c r="E5" t="s">
+        <v>15</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -600,8 +610,8 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>0</v>
+      <c r="E6" t="s">
+        <v>15</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -619,6 +629,181 @@
         <v>0</v>
       </c>
       <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>46112</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46112</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>0</v>
       </c>
     </row>
